--- a/data/export/2026-10-17-operations.xlsx
+++ b/data/export/2026-10-17-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -991,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,33 +1076,37 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1222,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2394,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2455,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,18 +2499,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2527,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2575,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2594,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2630,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2595,22 +2643,22 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2691,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2710,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2746,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2812,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2826,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2862,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2880,7 +2928,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2942,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2978,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2996,7 +3044,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3058,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3094,3051 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-operations.xlsx
+++ b/data/export/2026-10-17-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD48"/>
+  <dimension ref="A1:AD72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1139,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1559,7 +1583,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1603,32 +1627,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1636,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1688,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1791,7 +1823,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1835,32 +1867,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1868,7 +1904,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1892,17 +1928,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1912,17 +1948,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2027,7 +2063,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2042,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2183,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2162,7 +2198,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2380,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,13 +2424,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2500,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2509,40 +2549,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2575,12 +2615,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2594,7 +2634,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2619,46 +2659,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2691,12 +2735,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2710,7 +2754,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2735,46 +2779,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2807,12 +2855,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2826,7 +2874,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2851,7 +2899,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2862,35 +2910,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2923,12 +2971,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2942,7 +2990,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2967,7 +3015,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2978,35 +3026,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3039,12 +3087,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3058,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3083,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3155,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3174,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3199,46 +3251,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3271,12 +3327,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3290,7 +3346,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3315,18 +3371,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3339,60 +3399,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3406,7 +3470,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3416,33 +3480,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3455,60 +3523,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3522,7 +3594,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3532,33 +3604,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3647,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3581,7 +3657,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3591,40 +3667,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3638,7 +3718,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3648,17 +3728,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3668,13 +3748,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3687,22 +3771,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3735,12 +3819,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3754,7 +3838,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3790,7 +3874,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3887,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3813,7 +3897,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3851,12 +3935,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3870,7 +3954,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3895,7 +3979,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3906,7 +3990,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3919,22 +4003,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3967,12 +4051,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3986,7 +4070,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4022,7 +4106,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4035,22 +4119,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4083,12 +4167,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4102,7 +4186,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4138,7 +4222,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4235,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4161,7 +4245,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4199,12 +4283,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4218,7 +4302,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4254,7 +4338,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4267,22 +4351,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4315,12 +4399,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4334,7 +4418,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4370,7 +4454,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4467,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4393,7 +4477,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4436,7 +4520,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4450,7 +4534,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4486,7 +4570,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4583,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4509,7 +4593,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4547,12 +4631,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4566,7 +4650,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4602,7 +4686,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4615,22 +4699,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4663,12 +4747,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4682,7 +4766,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4718,7 +4802,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4815,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4741,7 +4825,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4779,12 +4863,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4798,7 +4882,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4834,35 +4918,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4895,12 +4979,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4914,7 +4998,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4939,7 +5023,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4950,77 +5034,73 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5034,7 +5114,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5044,107 +5124,99 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5158,7 +5230,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5168,17 +5240,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5188,87 +5260,79 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5282,7 +5346,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5292,17 +5356,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5312,45 +5376,41 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5383,12 +5443,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5402,7 +5462,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5438,35 +5498,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5499,12 +5559,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5518,7 +5578,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5554,35 +5614,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5615,12 +5675,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5634,7 +5694,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5670,35 +5730,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5736,7 +5796,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5750,7 +5810,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5775,7 +5835,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5786,35 +5846,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5847,12 +5907,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5866,7 +5926,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5902,35 +5962,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5963,12 +6023,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5982,7 +6042,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6018,35 +6078,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6079,12 +6139,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6098,47 +6158,2879 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X48" s="2" t="inlineStr">
+      <c r="X65" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y48" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA65" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
+      <c r="AB65" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
-      <c r="AD48" s="2" t="inlineStr">
-        <is>
-          <t>2/9</t>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-operations.xlsx
+++ b/data/export/2026-10-17-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD72"/>
+  <dimension ref="A1:AD90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1991,32 +1991,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2024,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,17 +2052,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2068,12 +2072,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2111,32 +2115,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2144,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2168,17 +2176,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2188,17 +2196,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2231,32 +2239,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2264,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2288,33 +2300,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2347,32 +2363,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2380,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2404,37 +2424,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2467,32 +2487,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2500,7 +2524,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2524,37 +2548,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2587,32 +2611,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2620,7 +2648,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2644,37 +2672,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2707,32 +2735,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2740,7 +2772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2764,37 +2796,37 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2892,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2976,7 +3008,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3092,7 +3124,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3146,7 +3178,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3244,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3256,12 +3288,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
@@ -3279,22 +3311,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3327,12 +3359,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3346,7 +3378,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3371,7 +3403,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3381,82 +3413,78 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3470,7 +3498,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3480,107 +3508,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>114分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3594,7 +3618,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3604,107 +3628,103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3718,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3728,65 +3748,65 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3819,12 +3839,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3838,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3863,46 +3883,50 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3935,12 +3959,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3954,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3979,18 +4003,22 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4003,52 +4031,56 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4056,7 +4088,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4070,7 +4102,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4080,33 +4112,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4119,60 +4155,64 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4186,7 +4226,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4196,33 +4236,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4235,60 +4279,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4302,7 +4350,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4312,33 +4360,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4403,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4361,7 +4413,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4371,40 +4423,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4418,7 +4474,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4428,33 +4484,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4467,22 +4527,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4515,12 +4575,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4534,7 +4594,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4559,7 +4619,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4570,7 +4630,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4643,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4593,7 +4653,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4603,40 +4663,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4650,7 +4714,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4660,33 +4724,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4699,60 +4767,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4766,7 +4838,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4776,33 +4848,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4815,22 +4891,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4863,12 +4939,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4882,7 +4958,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4907,7 +4983,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4918,7 +4994,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4931,60 +5007,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4998,7 +5078,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5008,17 +5088,17 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5028,13 +5108,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5047,60 +5131,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5114,7 +5202,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5124,17 +5212,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5144,13 +5232,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5255,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5173,7 +5265,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5211,12 +5303,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5230,7 +5322,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5255,7 +5347,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5266,7 +5358,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5279,32 +5371,32 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:36</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5327,12 +5419,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5340,13 +5432,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5382,7 +5490,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5395,22 +5503,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5443,12 +5551,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5462,7 +5570,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5498,7 +5606,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5511,22 +5619,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5559,12 +5667,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5578,7 +5686,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5614,7 +5722,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5735,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5637,7 +5745,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5647,12 +5755,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq50，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5675,12 +5783,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5688,13 +5796,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq39（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5730,7 +5854,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5867,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5753,7 +5877,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5791,12 +5915,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5810,7 +5934,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5846,7 +5970,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5983,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5869,7 +5993,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5907,12 +6031,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5926,7 +6050,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5962,7 +6086,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5975,22 +6099,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6023,12 +6147,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6042,7 +6166,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6078,7 +6202,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6091,22 +6215,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6139,12 +6263,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6158,7 +6282,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6194,7 +6318,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6331,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6217,7 +6341,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6255,12 +6379,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6274,7 +6398,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6310,7 +6434,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6323,22 +6447,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6376,7 +6500,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6390,7 +6514,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6426,7 +6550,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6439,22 +6563,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6487,12 +6611,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6506,7 +6630,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6531,22 +6655,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6679,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6569,7 +6689,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6612,7 +6732,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6626,7 +6746,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6651,22 +6771,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6795,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6689,7 +6805,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6727,12 +6843,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6746,7 +6862,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6782,7 +6898,7 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6795,22 +6911,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6848,7 +6964,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6862,7 +6978,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6887,7 +7003,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6898,35 +7014,35 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6964,7 +7080,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6978,7 +7094,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7003,7 +7119,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7014,77 +7130,73 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7098,7 +7210,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7108,17 +7220,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7133,40 +7245,40 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7204,7 +7316,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7218,7 +7330,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7248,83 +7360,83 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7338,7 +7450,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7348,65 +7460,61 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7444,7 +7552,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7458,7 +7566,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7488,75 +7596,75 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7564,7 +7672,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7578,7 +7686,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7588,17 +7696,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7608,87 +7716,79 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7702,7 +7802,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7712,65 +7812,65 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7808,7 +7908,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7822,7 +7922,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7852,41 +7952,45 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7919,12 +8023,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7938,7 +8042,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7963,7 +8067,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7974,35 +8078,35 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8035,12 +8139,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8054,7 +8158,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8079,46 +8183,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A92076D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8151,12 +8259,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8170,7 +8278,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8195,50 +8303,46 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8271,12 +8375,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8290,7 +8394,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8326,7 +8430,7 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8339,22 +8443,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8387,12 +8491,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8406,7 +8510,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8431,18 +8535,22 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8455,52 +8563,56 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8508,7 +8620,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8522,7 +8634,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8532,17 +8644,17 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8557,12 +8669,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8687,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8585,7 +8697,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8623,12 +8735,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8642,7 +8754,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8667,7 +8779,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8678,7 +8790,7 @@
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8803,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8701,7 +8813,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8711,40 +8823,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8758,7 +8874,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8768,17 +8884,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8788,13 +8904,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8807,60 +8927,64 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8874,7 +8998,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8884,33 +9008,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8928,47 +9056,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8976,7 +9108,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8990,47 +9122,2187 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB84" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AD72" s="2" t="inlineStr">
-        <is>
-          <t>4/12</t>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-operations.xlsx
+++ b/data/export/2026-10-17-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2328,17 +2328,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3444,17 +3444,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4312,17 +4312,17 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6788,17 +6788,17 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7284,17 +7284,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7780,17 +7780,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8272,17 +8272,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9512,17 +9512,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9689,24 +9689,24 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9927,32 +9927,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9960,7 +9964,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9984,17 +9988,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10004,12 +10008,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10047,32 +10051,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -10080,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10104,17 +10112,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10124,17 +10132,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -10167,32 +10175,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -10200,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10224,17 +10236,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10244,17 +10256,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10332,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10369,12 +10381,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10452,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10484,12 +10496,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10742,7 +10754,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10824,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10866,7 +10878,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11316,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11478,7 +11490,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11684,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11796,7 +11808,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11840,17 +11852,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11998,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12118,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12188,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12220,12 +12232,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12296,7 +12308,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12366,7 +12378,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12696,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12738,7 +12750,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12820,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12932,7 +12944,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12986,7 +12998,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13068,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13180,7 +13192,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13229,12 +13241,12 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13370,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13440,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13552,7 +13564,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13596,17 +13608,17 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13742,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13990,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -14048,7 +14060,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14102,7 +14114,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14180,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14222,7 +14234,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14726,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14784,7 +14796,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -15164,7 +15176,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15208,17 +15220,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15300,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15412,7 +15424,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15456,12 +15468,12 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
@@ -15590,7 +15602,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -15908,7 +15920,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15962,7 +15974,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16044,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16156,7 +16168,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16210,7 +16222,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16292,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16329,12 +16341,12 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -16404,7 +16416,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16582,7 +16594,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16788,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16830,7 +16842,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -17198,7 +17210,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17590,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17710,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17780,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17822,7 +17834,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -18140,7 +18152,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18189,12 +18201,12 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18276,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18318,7 +18330,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -18566,7 +18578,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18702,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -18938,7 +18950,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19062,7 +19074,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -19442,7 +19454,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -19512,7 +19524,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19556,17 +19568,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19648,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19760,7 +19772,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19804,17 +19816,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19896,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19928,12 +19940,12 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -20008,7 +20020,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20062,7 +20074,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -20132,7 +20144,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20186,7 +20198,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20268,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20310,7 +20322,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -20380,7 +20392,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20500,7 +20512,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20624,7 +20636,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20678,7 +20690,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20760,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -21050,7 +21062,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21186,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -21298,7 +21310,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21678,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -21864,7 +21876,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21961,24 +21973,24 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
@@ -21988,7 +22000,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22037,12 +22049,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22075,32 +22087,36 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -22108,7 +22124,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22132,17 +22148,17 @@
       </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA175" s="2" t="inlineStr">
@@ -22152,13 +22168,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC175" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC175" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -22213,12 +22233,12 @@
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O176" s="2" t="inlineStr">
@@ -22228,7 +22248,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22315,32 +22335,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -22348,7 +22372,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22372,17 +22396,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22392,17 +22416,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -22435,12 +22459,12 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -22468,7 +22492,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22476,10 +22500,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R178" s="2" t="inlineStr"/>
-      <c r="S178" s="2" t="inlineStr"/>
-      <c r="T178" s="2" t="inlineStr"/>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22555,32 +22595,36 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N179" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22588,7 +22632,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22612,17 +22656,17 @@
       </c>
       <c r="X179" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA179" s="2" t="inlineStr">
@@ -22632,17 +22676,17 @@
       </c>
       <c r="AB179" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -22675,32 +22719,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -22708,7 +22756,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22732,17 +22780,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22752,12 +22800,12 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
@@ -22795,12 +22843,12 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -22828,7 +22876,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22836,10 +22884,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R181" s="2" t="inlineStr"/>
-      <c r="S181" s="2" t="inlineStr"/>
-      <c r="T181" s="2" t="inlineStr"/>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V181" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -22882,7 +22946,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -22948,7 +23012,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23002,7 +23066,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23132,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23122,7 +23186,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23252,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23242,7 +23306,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23372,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23362,7 +23426,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -23428,7 +23492,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23548,7 +23612,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23668,7 +23732,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23842,7 +23906,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -24086,7 +24150,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24646,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -24706,7 +24770,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -24900,7 +24964,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24949,7 +25013,7 @@
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
@@ -25198,7 +25262,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -25268,7 +25332,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25312,17 +25376,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -25760,7 +25824,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25804,17 +25868,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26064,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26044,17 +26108,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -26120,7 +26184,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26164,17 +26228,17 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -26298,7 +26362,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26606,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26800,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26785,7 +26849,7 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
@@ -27034,7 +27098,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27292,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27272,17 +27336,17 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -27476,7 +27540,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27520,17 +27584,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -27600,7 +27664,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27644,17 +27708,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -27778,7 +27842,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27912,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27892,17 +27956,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -27972,7 +28036,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28021,7 +28085,7 @@
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
@@ -28150,7 +28214,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -28274,7 +28338,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -28344,7 +28408,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28388,17 +28452,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28652,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28632,17 +28696,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -28836,7 +28900,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28880,17 +28944,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -28960,7 +29024,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29004,17 +29068,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29202,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -29208,7 +29272,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29252,12 +29316,12 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
@@ -29828,7 +29892,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29872,17 +29936,17 @@
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30076,7 +30140,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30120,12 +30184,12 @@
       </c>
       <c r="AB240" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
@@ -30200,7 +30264,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30249,7 +30313,7 @@
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
@@ -30378,7 +30442,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -30692,7 +30756,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30736,17 +30800,17 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -30940,7 +31004,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -30984,17 +31048,17 @@
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -31432,7 +31496,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31476,17 +31540,17 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -31556,7 +31620,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31605,7 +31669,7 @@
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
@@ -31680,7 +31744,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31724,17 +31788,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -31858,7 +31922,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -31928,7 +31992,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -31972,12 +32036,12 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
@@ -32230,7 +32294,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -32354,7 +32418,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -32424,7 +32488,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32468,17 +32532,17 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -32672,7 +32736,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32716,17 +32780,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -33292,7 +33356,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33336,17 +33400,17 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -33416,7 +33480,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33460,17 +33524,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -33540,7 +33604,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33589,7 +33653,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33664,7 +33728,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33708,12 +33772,12 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
@@ -33838,7 +33902,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -33962,7 +34026,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -34206,7 +34270,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -34276,7 +34340,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34320,17 +34384,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -34524,7 +34588,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34568,17 +34632,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -35103,32 +35167,36 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N281" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O281" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35136,7 +35204,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35160,17 +35228,17 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA281" s="2" t="inlineStr">
@@ -35180,17 +35248,17 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -35310,7 +35378,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35498,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -35473,24 +35541,24 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O284" s="2" t="inlineStr">
@@ -35500,7 +35568,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35549,7 +35617,7 @@
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35587,32 +35655,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O285" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35620,7 +35692,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35644,17 +35716,17 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA285" s="2" t="inlineStr">
@@ -35664,17 +35736,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -35707,32 +35779,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -35740,7 +35816,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35764,17 +35840,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35784,12 +35860,12 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -35827,32 +35903,36 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N287" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O287" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35860,7 +35940,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35884,17 +35964,17 @@
       </c>
       <c r="X287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA287" s="2" t="inlineStr">
@@ -35904,17 +35984,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -35947,32 +36027,36 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N288" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O288" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -35980,7 +36064,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36004,17 +36088,17 @@
       </c>
       <c r="X288" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA288" s="2" t="inlineStr">
@@ -36024,17 +36108,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -36100,7 +36184,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36144,17 +36228,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -36220,7 +36304,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36264,12 +36348,12 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">

--- a/data/export/2026-10-17-operations.xlsx
+++ b/data/export/2026-10-17-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2824,17 +2824,17 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3940,17 +3940,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9760,17 +9760,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10299,32 +10299,36 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10332,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10356,17 +10360,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10376,17 +10380,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -10419,32 +10423,36 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10452,7 +10460,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10476,17 +10484,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10496,12 +10504,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10754,7 +10762,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10832,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10868,17 +10876,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11254,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11324,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11490,7 +11498,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11862,7 +11870,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12704,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12740,17 +12748,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -12820,7 +12828,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12864,12 +12872,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
@@ -12944,7 +12952,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13618,7 +13626,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13998,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14068,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14180,7 +14188,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14224,17 +14232,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14610,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14734,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14804,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -15230,7 +15238,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -15300,7 +15308,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15920,7 +15928,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15964,17 +15972,17 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16052,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16088,12 +16096,12 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
@@ -16168,7 +16176,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16788,7 +16796,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -17210,7 +17218,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -18276,7 +18284,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18950,7 +18958,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19082,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -19198,7 +19206,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -19578,7 +19586,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19826,7 +19834,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -20144,7 +20152,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20188,17 +20196,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20276,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20312,17 +20320,17 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -20512,7 +20520,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20636,7 +20644,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20760,7 +20768,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -21310,7 +21318,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21566,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -21876,7 +21884,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21920,12 +21928,12 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
@@ -22426,7 +22434,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -22686,7 +22694,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -22848,7 +22856,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -22876,7 +22884,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -23099,32 +23107,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23132,7 +23144,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23156,17 +23168,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23176,17 +23188,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -23219,32 +23231,36 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23252,7 +23268,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23276,17 +23292,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23296,17 +23312,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23388,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23492,7 +23508,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23612,7 +23628,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23699,32 +23715,36 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>58分钟</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N188" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -23732,7 +23752,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23756,17 +23776,17 @@
       </c>
       <c r="X188" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA188" s="2" t="inlineStr">
@@ -23776,12 +23796,12 @@
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
@@ -25630,7 +25650,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -25824,7 +25844,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25873,12 +25893,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -26064,7 +26084,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26108,12 +26128,12 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -27222,7 +27242,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -27540,7 +27560,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27589,12 +27609,12 @@
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -27912,7 +27932,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27956,12 +27976,12 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
@@ -28652,7 +28672,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28701,12 +28721,12 @@
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -28830,7 +28850,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -28900,7 +28920,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28944,12 +28964,12 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
@@ -29272,7 +29292,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29698,7 +29718,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -30140,7 +30160,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -31004,7 +31024,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31053,12 +31073,12 @@
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -31306,7 +31326,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -31744,7 +31764,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31788,12 +31808,12 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
@@ -31992,7 +32012,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32736,7 +32756,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32785,12 +32805,12 @@
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -33038,7 +33058,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -33480,7 +33500,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33524,12 +33544,12 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
@@ -33728,7 +33748,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -34588,7 +34608,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34637,12 +34657,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -34890,7 +34910,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -35692,7 +35712,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35736,12 +35756,12 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35816,7 +35836,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -36037,12 +36057,12 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
@@ -36064,7 +36084,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36113,12 +36133,12 @@
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -36151,32 +36171,36 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr"/>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N289" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O289" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -36184,7 +36208,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36208,17 +36232,17 @@
       </c>
       <c r="X289" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z289" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA289" s="2" t="inlineStr">
@@ -36228,12 +36252,12 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36304,7 +36328,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
